--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DFS_HRM-2031-0432/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DFS_HRM-2031-0432/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.70076</v>
+        <v>17.15157</v>
       </c>
       <c r="D2" t="n">
-        <v>16.7831</v>
+        <v>16.80379</v>
       </c>
       <c r="E2" t="n">
-        <v>16.86837</v>
+        <v>16.87976</v>
       </c>
       <c r="F2" t="n">
-        <v>43.25812</v>
+        <v>42.70182</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05064</v>
+        <v>0.05162</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83979</v>
+        <v>1.794</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.17187</v>
+        <v>17.07115</v>
       </c>
       <c r="D3" t="n">
-        <v>16.67953</v>
+        <v>16.79059</v>
       </c>
       <c r="E3" t="n">
-        <v>17.03541</v>
+        <v>16.98232</v>
       </c>
       <c r="F3" t="n">
-        <v>43.30565</v>
+        <v>42.55263</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05108</v>
+        <v>0.05167</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81106</v>
+        <v>1.86585</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.96913</v>
+        <v>17.24131</v>
       </c>
       <c r="D4" t="n">
-        <v>16.62859</v>
+        <v>16.59644</v>
       </c>
       <c r="E4" t="n">
-        <v>16.95941</v>
+        <v>17.05972</v>
       </c>
       <c r="F4" t="n">
-        <v>43.19362</v>
+        <v>43.23859</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05168</v>
+        <v>0.05211</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8017</v>
+        <v>1.86845</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.00906</v>
+        <v>16.5613</v>
       </c>
       <c r="D6" t="n">
-        <v>16.04759</v>
+        <v>15.9404</v>
       </c>
       <c r="E6" t="n">
-        <v>16.95665</v>
+        <v>16.48927</v>
       </c>
       <c r="F6" t="n">
-        <v>22.24977</v>
+        <v>22.24991</v>
       </c>
       <c r="G6" t="n">
-        <v>34.33273</v>
+        <v>34.85479</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.78343</v>
+        <v>17.12486</v>
       </c>
       <c r="D7" t="n">
-        <v>16.14904</v>
+        <v>16.29851</v>
       </c>
       <c r="E7" t="n">
-        <v>16.4104</v>
+        <v>16.70198</v>
       </c>
       <c r="F7" t="n">
-        <v>22.2149</v>
+        <v>21.60877</v>
       </c>
       <c r="G7" t="n">
-        <v>34.92711</v>
+        <v>34.54374</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.8995</v>
+        <v>16.98451</v>
       </c>
       <c r="D8" t="n">
-        <v>16.20909</v>
+        <v>16.37538</v>
       </c>
       <c r="E8" t="n">
-        <v>16.763</v>
+        <v>16.59728</v>
       </c>
       <c r="F8" t="n">
-        <v>21.80126</v>
+        <v>22.0823</v>
       </c>
       <c r="G8" t="n">
-        <v>34.72298</v>
+        <v>34.35323</v>
       </c>
     </row>
   </sheetData>
